--- a/.playwright-mcp/Patient.xlsx
+++ b/.playwright-mcp/Patient.xlsx
@@ -13,10 +13,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20002" uniqueCount="118">
   <si>
-    <t>First Name</t>
+    <t>FName</t>
   </si>
   <si>
-    <t>Last Name</t>
+    <t>LName</t>
   </si>
   <si>
     <t>Erika</t>
@@ -371,7 +371,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -383,10 +383,7 @@
       <color rgb="FFFFFFFF"/>
     </font>
     <font>
-      <color rgb="FFEEF2F6"/>
-    </font>
-    <font>
-      <color rgb="FFF5F7F9"/>
+      <color rgb="FF334155"/>
     </font>
   </fonts>
   <fills count="5">
@@ -403,12 +400,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA12121"/>
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2C5987"/>
+        <fgColor rgb="FFF8FAFC"/>
       </patternFill>
     </fill>
   </fills>
@@ -422,16 +419,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F79C6"/>
+        <color rgb="FFE2E8F0"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F79C6"/>
+        <color rgb="FFE2E8F0"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F79C6"/>
+        <color rgb="FFE2E8F0"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F79C6"/>
+        <color rgb="FFE2E8F0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -443,7 +440,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -786,7 +783,7 @@
   <dimension ref="A1:B10001"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
   </cols>
   <sheetData>
